--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260820.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260820.xlsx
@@ -887,17 +887,17 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>5,540,296</t>
+          <t>5,407,520</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -909,17 +909,17 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>5,407,520</t>
+          <t>5,540,296</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>615,600</t>
+          <t>875,349</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1107,17 +1107,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>875,349</t>
+          <t>615,600</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>1,871,000</t>
+          <t>5,840,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>3,289,000</t>
+          <t>1,871,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>5,840,000</t>
+          <t>3,289,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>仁寶</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>7,318,249</t>
+          <t>4,546,578</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>仁寶</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>4,546,578</t>
+          <t>7,318,249</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>10,821,121</t>
+          <t>2,651,703</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>2,651,703</t>
+          <t>594,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>594,000</t>
+          <t>10,821,121</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>1,210,076</t>
+          <t>95,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1723,17 +1723,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>95,000</t>
+          <t>1,210,076</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>5,063,956</t>
+          <t>792,000</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1789,17 +1789,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>821,000</t>
+          <t>296,000</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>792,000</t>
+          <t>232,000</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1833,17 +1833,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>296,000</t>
+          <t>821,000</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -1855,17 +1855,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>禾伸堂</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>232,000</t>
+          <t>5,063,956</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -1877,17 +1877,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>神達</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>1,592,400</t>
+          <t>508,000</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -1899,17 +1899,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>神達</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>508,000</t>
+          <t>1,592,400</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -1943,17 +1943,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>1,024,121</t>
+          <t>117,000</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>117,000</t>
+          <t>1,024,121</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>338,000</t>
+          <t>66,538</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>66,538</t>
+          <t>338,000</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2097,17 +2097,17 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>182,000</t>
+          <t>694,000</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -2141,17 +2141,17 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>694,000</t>
+          <t>182,000</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
